--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk1pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk1pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.9</t>
+          <t>00:009.8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:019.8</t>
+          <t>00:020.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.1</t>
+          <t>00:029.9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.2</t>
+          <t>00:039.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,44 +687,44 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>222204</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.1</t>
+          <t>00:049.8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>433270</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450249</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.0</t>
+          <t>01:010.2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409981</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.8</t>
+          <t>01:020.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.10</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>346439</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -937,17 +937,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>319170</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -989,22 +989,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.2</t>
+          <t>01:040.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.46</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288783</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.1</t>
+          <t>01:049.9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>300924</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370550</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.8</t>
+          <t>02:010.1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>381991</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.0</t>
+          <t>02:019.9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>64.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>425816</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>63.1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>456648</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:040.1</t>
+          <t>02:040.3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>378813</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.0</t>
+          <t>02:049.7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>275682</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.9</t>
+          <t>02:054.8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,22 +1475,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>226780</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk1pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk1pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.8</t>
+          <t>00:010.3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.0</t>
+          <t>00:019.6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>100.14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127785</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.9</t>
+          <t>00:030.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>120.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>325525</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -640,34 +640,34 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.2</t>
+          <t>00:039.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>222204</t>
+          <t>387957</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -697,34 +697,34 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.8</t>
+          <t>00:050.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>102.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>433270</t>
+          <t>363983</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>450249</t>
+          <t>343653</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.2</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>409981</t>
+          <t>343096</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>346439</t>
+          <t>355212</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.8</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>319170</t>
+          <t>358352</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,22 +994,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>11.33</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>288783</t>
+          <t>398500</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>300924</t>
+          <t>527594</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -1108,22 +1108,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>370550</t>
+          <t>684006</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.1</t>
+          <t>02:010.2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>381991</t>
+          <t>784509</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:020.0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>425816</t>
+          <t>849632</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>63.1</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>456648</t>
+          <t>962074</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:040.3</t>
+          <t>02:040.1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>378813</t>
+          <t>1007688</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,12 +1388,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.7</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>275682</t>
+          <t>951775</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,55 +1445,112 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.8</t>
+          <t>02:055.2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>923758</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>20.2</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4.79</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>226780</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>922544</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>
